--- a/光伏配储项目/电价数据/2026/河东站.xlsx
+++ b/光伏配储项目/电价数据/2026/河东站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50989</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7206</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5646599999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.51612</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45339</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44803</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43786</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45468</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42326</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26789</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.21415</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.25833</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07684999999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06309000000000001</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05126</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.03181</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.05299</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03897</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04453</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.007820000000000001</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.01818</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.0862</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.01498</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.00172</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00354</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14522</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21298</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23615</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.2135</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.11493</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.004990000000000001</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00695</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.15492</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.19248</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.19049</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22301</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.21974</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.12235</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.1937</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.26289</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.00983</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.23297</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.01286</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.44961</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.46361</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.52642</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.48055</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.7598200000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.61456</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.5087200000000001</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.50444</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.11854</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.58414</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5404500000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.25591</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.49835</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.50171</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6126200000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.56884</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.4324</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.49632</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.44975</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6219199999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.42682</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.75561</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.1401</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8524700000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.54534</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5274500000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50762</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51474</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.51084</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39476</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47715</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42526</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5276799999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6535</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7506499999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38866</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44629</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.08710999999999999</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.26186</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.26848</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.25443</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.5878300000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.19339</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.27589</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.26669</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.57973</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.02189</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.2685</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.22836</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.15763</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.2312</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.25582</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.26265</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.43606</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.42161</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.26196</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.46505</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.27676</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.7075900000000001</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.90454</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.86934</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.26199</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.84427</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.42091</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.38397</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.81996</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43811</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.5981599999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43914</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4338</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.34224</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5365700000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.40735</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40914</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47401</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44852</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44289</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40388</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37368</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28483</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.1588</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.4227</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.46925</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.3762200000000001</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.43323</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.44338</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.26665</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.06818</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.21421</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.1452</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.20356</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24721</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.28822</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.28394</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.24342</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.2097</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.03801</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.28028</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.47545</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.03086</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.49845</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.28359</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.28293</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.29878</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34406</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.27244</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.27573</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47847</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.27574</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.28229</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.28422</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.28094</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.28163</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.28155</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36413</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29784</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.28033</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.26299</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26388</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.19331</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.10796</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11086</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08094</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.2511</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.21304</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.12881</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.44698</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.21053</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.04747999999999999</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.04831000000000001</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06118999999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.26858</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.17685</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.04011</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.01286</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21326</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.00237</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.02986</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.04682</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.07629999999999999</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.20464</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.16782</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.20437</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.15318</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19774</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14328</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.20184</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.22867</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.27973</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.25679</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28584</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.47076</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.38274</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.29813</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.29776</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.25673</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29211</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.27597</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.27435</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.27715</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26047</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04515</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04025</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04509000000000001</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04358</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04559000000000001</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04616</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04708</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04782</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04631</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04664</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04749</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04669</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.0457</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04787</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04986</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04639</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04783</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04906</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04867</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04638</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04728</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22004</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04649</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04902</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05177</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00215</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14705</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03754</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09884</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41226</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41732</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35132</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66437</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44655</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10243</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04262</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04592</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04487</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04487</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04403</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04185</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03233</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04071</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10692</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00104</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03742</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04689</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04114</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04131</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04122</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04377</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04112</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04053</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04331</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04038</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03901</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04405</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04375</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04111</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04219</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04267</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04308</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04645000000000001</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04604999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20231</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14478</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29752</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29628</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29967</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27135</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29629</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33772</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32283</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40733</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28354</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29052</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27349</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27363</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28336</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17433</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.16059</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17322</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14956</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16128</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.16066</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23955</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21609</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22869</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27196</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28851</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.2931</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28328</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27079</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28316</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.38549</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.4169</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38203</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.46598</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.56359</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.45358</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.44915</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.42611</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15729</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.40668</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7910900000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6219199999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78086</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.9200199999999999</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49429</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9278099999999999</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.90613</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31906</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.92925</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63867</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.22811</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8891</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.57992</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.37292</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0618</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.82685</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.8090499999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.80613</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.88121</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.89271</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5268400000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.43157</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.44315</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4884</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.25025</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.88005</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55176</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.66477</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54901</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.51004</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46108</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42932</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44473</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45199</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45325</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42234</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40046</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41532</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43437</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.37573</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45132</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5896399999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42854</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59684</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6019800000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.64538</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45459</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.44015</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.63635</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44734</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.86491</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.80998</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.90266</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.88671</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8827</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43416</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.41111</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.47112</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27321</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45282</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35329</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.0234</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.49896</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.49932</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.61653</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.69064</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40992</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.44843</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.50886</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.44651</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50064</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28911</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28055</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16473</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26108</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20116</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27748</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.47514</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27589</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37535</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29103</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.25024</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27497</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42837</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.24723</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44705</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5976699999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88976</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35719</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13675</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7115900000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8055599999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6513300000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.59076</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45103</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50043</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43989</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43763</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42368</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5009100000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43407</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43409</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42833</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45076</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39633</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43443</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.79698</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.41036</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.16458</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.67196</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.40443</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.01848</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.94077</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.23714</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.36303</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.5976399999999999</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.7926299999999999</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.27224</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26844</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.48984</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.39538</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29766</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.4843</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.4302</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.60665</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46567</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.6860499999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46668</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42557</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38814</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3265</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42568</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39369</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.10518</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23713</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14644</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14911</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15606</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14478</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14227</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14481</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14371</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25888</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14544</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26859</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14329</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05214</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11477</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11371</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14748</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.1425</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14774</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45139</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39362</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43798</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44178</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44122</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44617</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44544</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40423</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35067</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5920299999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47033</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41742</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38258</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.5541200000000001</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.38583</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.22169</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.27703</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44476</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.45736</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24911</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.42433</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.50901</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36064</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28417</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.42285</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.45108</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44094</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.28832</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26933</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03374</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25394</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24997</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.20893</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07462000000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18373</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24485</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28618</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.27059</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25265</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27392</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42693</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.5039</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.77476</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.44814</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46628</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.4314</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30966</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.41432</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28258</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28716</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37793</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.35103</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.41096</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.7290099999999999</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.41489</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38271</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42958</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64959</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8749400000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48671</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.48285</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46037</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34507</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41164</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36317</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26134</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13594</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28412</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28267</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24612</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27854</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.02331</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27961</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.12975</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28404</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23704</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28738</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24734</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30321</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.01239</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.1449</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29941</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.02763</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.23193</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.23517</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40808</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6396900000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60798</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.58813</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46225</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.59104</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47729</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.73222</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45307</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.45964</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.4816</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43058</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41995</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3602</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49318</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.47234</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4654</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.45632</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.4214</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40096</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40737</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41132</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4197</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41144</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38803</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41904</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41723</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44997</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56126</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5008899999999999</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45095</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.41141</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4193</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42727</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42286</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.15043</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.03746</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.02889</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.43122</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.86424</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.15454</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.1043</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.26706</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.03129</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41436</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48582</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.44119</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5083799999999999</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.4258</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.57994</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.66948</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.6496900000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.6304500000000001</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.70009</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.51555</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.50485</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.76991</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.71231</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.57885</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.62286</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.40572</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.41487</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.46836</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.46516</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.45864</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5147999999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41717</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.43465</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44837</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42943</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42016</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44451</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44917</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40302</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39553</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15794</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.27142</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03683</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40862</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45317</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40999</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46413</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01558</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18515</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38236</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37348</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39548</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37325</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36281</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44376</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.43494</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.45104</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24739</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23533</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23703</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24554</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25172</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.03709</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.16838</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.27592</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.05351</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.17493</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25924</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.03682</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14838</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15244</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.05686</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.25037</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.24611</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.45492</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37382</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35387</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19466</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.18697</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.13234</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.15171</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01612</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00155</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.04361</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.04946</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04152</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.00882</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.14065</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.19238</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2768</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.22442</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.22511</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22593</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.23021</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.24068</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.26732</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.25026</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.24377</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.23484</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.25101</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25466</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.23762</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.25575</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.24431</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.26164</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.24966</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.26334</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.27722</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.27755</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.26004</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.2201</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.23993</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.21821</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.18866</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.09003</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.03292</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.24841</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.03968</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.1611</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.15915</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.15944</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.03052</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.23556</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.21885</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.20375</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16824</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15964</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.13562</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.15973</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.19057</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.11285</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.12715</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.19287</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.16353</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.21249</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.18591</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.17326</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.2235</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.17362</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.22411</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.29293</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.23075</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.2124</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.21882</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.13401</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.44886</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.20651</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.00337</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.17356</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.16932</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.01517</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04078</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.01965</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.18817</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.04909</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.26769</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.03112</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.04989</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.08409999999999999</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04989</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.04214</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.04907</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.01681</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.04899</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.04199</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23408</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28022</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25178</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.19018</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32621</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.10578</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.26477</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.41375</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.25474</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25139</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.11605</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24104</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43954</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.16189</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25587</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26981</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.18779</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14357</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.10329</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37263</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33209</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.2421</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.26526</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3739</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.27292</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5942000000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5921000000000001</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.25149</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.27227</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28287</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.26586</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.16769</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26044</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.26611</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26525</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26246</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.24594</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.28059</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.39132</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.46504</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.4705299999999999</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.5453</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.58323</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.58075</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.51851</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.0506</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.38983</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.42672</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.46145</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40379</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.5418200000000001</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.47411</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38761</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45217</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43091</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.87271</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.49597</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.42712</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.4513</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40287</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36903</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46717</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.28698</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.45364</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.30321</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.20472</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.17475</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23359</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29111</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.25927</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.19181</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.26297</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.27365</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.45952</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39354</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39068</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46508</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.55965</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5596100000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.4617</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.55143</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46403</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49654</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.53234</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.52018</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.71405</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.75887</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.54947</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5521</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44479</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3757200000000001</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2725</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.27249</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.26934</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.28096</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.2682</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.26387</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.25642</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.24958</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.23921</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.23784</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.25494</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.19086</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.21307</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.13219</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.04768</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.16281</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01192</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.12396</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.00265</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.01805</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01379</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02313</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.02784</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23526</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.01721</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02137</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03134</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02196</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01764</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.02903</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.10526</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11936</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.13662</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.16425</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.22356</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18142</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.18399</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.20825</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.2511</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40467</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41831</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38776</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38442</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38426</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39883</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38063</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.74336</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38395</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.29116</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.28495</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.27175</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.26126</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.23309</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22669</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.19576</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.19577</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.20015</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.21661</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.10787</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01536</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01286</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01229</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03617</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.07903</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.05122</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00435</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02249</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02229</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.02909</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15565</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.22213</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04635</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.18453</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.17925</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.13683</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.19443</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.15094</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.19018</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.22435</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.18381</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.23675</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.26784</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38111</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39306</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38645</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5279199999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41408</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40843</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43148</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38701</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.51227</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41733</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.27249</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.23276</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.18787</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.17287</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.11324</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.14904</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.17558</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.16314</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.08796</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.10511</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04731</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.07067</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03606</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03687</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03749</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03621</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05219</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.0601</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03512</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.05709</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.07249</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.11569</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.14504</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.08716</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.16519</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.14642</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.09013</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04626</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21549</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.09691</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.18816</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.13141</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.14138</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.16841</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.14755</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.18235</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.20146</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.20247</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.2153</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.25574</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.25969</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.26127</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.2834100000000001</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40339</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.27409</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.41309</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41925</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49725</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41811</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44261</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39721</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4152</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41444</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38228</v>
       </c>
     </row>
   </sheetData>
